--- a/2d/results/best_unet_filter_distance_mean/best_unet.xlsx
+++ b/2d/results/best_unet_filter_distance_mean/best_unet.xlsx
@@ -535,10 +535,10 @@
         <v>140</v>
       </c>
       <c r="C2" t="n">
+        <v>17.69533182897614</v>
+      </c>
+      <c r="D2" t="n">
         <v>10.36121209728514</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.69533182897614</v>
       </c>
       <c r="E2" t="n">
         <v>16.48624936168851</v>
@@ -596,10 +596,10 @@
         <v>141</v>
       </c>
       <c r="C3" t="n">
+        <v>13.4683426988474</v>
+      </c>
+      <c r="D3" t="n">
         <v>15.22204953483589</v>
-      </c>
-      <c r="D3" t="n">
-        <v>13.4683426988474</v>
       </c>
       <c r="E3" t="n">
         <v>26.64504063529104</v>
@@ -657,10 +657,10 @@
         <v>149</v>
       </c>
       <c r="C4" t="n">
+        <v>12.16007904670465</v>
+      </c>
+      <c r="D4" t="n">
         <v>8.090673737281389</v>
-      </c>
-      <c r="D4" t="n">
-        <v>12.16007904670465</v>
       </c>
       <c r="E4" t="n">
         <v>15.66711742168132</v>
@@ -718,10 +718,10 @@
         <v>160</v>
       </c>
       <c r="C5" t="n">
+        <v>17.60449162329438</v>
+      </c>
+      <c r="D5" t="n">
         <v>14.4868285050769</v>
-      </c>
-      <c r="D5" t="n">
-        <v>17.60449162329438</v>
       </c>
       <c r="E5" t="n">
         <v>31.93707489464807</v>
@@ -779,10 +779,10 @@
         <v>170</v>
       </c>
       <c r="C6" t="n">
+        <v>14.50410218552473</v>
+      </c>
+      <c r="D6" t="n">
         <v>5.029244698309951</v>
-      </c>
-      <c r="D6" t="n">
-        <v>14.50410218552473</v>
       </c>
       <c r="E6" t="n">
         <v>17.4557046261906</v>
@@ -840,10 +840,10 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
+        <v>12.84127188044712</v>
+      </c>
+      <c r="D7" t="n">
         <v>11.7110096950743</v>
-      </c>
-      <c r="D7" t="n">
-        <v>12.84127188044712</v>
       </c>
       <c r="E7" t="n">
         <v>23.53030699293057</v>
@@ -901,10 +901,10 @@
         <v>190</v>
       </c>
       <c r="C8" t="n">
+        <v>11.61311947354066</v>
+      </c>
+      <c r="D8" t="n">
         <v>7.464319579834848</v>
-      </c>
-      <c r="D8" t="n">
-        <v>11.61311947354066</v>
       </c>
       <c r="E8" t="n">
         <v>31.18077765179081</v>
@@ -962,10 +962,10 @@
         <v>198</v>
       </c>
       <c r="C9" t="n">
+        <v>22.13594795868543</v>
+      </c>
+      <c r="D9" t="n">
         <v>14.5112818459411</v>
-      </c>
-      <c r="D9" t="n">
-        <v>22.13594795868543</v>
       </c>
       <c r="E9" t="n">
         <v>20.64468102444152</v>
@@ -1023,10 +1023,10 @@
         <v>199</v>
       </c>
       <c r="C10" t="n">
+        <v>14.73334678831316</v>
+      </c>
+      <c r="D10" t="n">
         <v>11.35393886517912</v>
-      </c>
-      <c r="D10" t="n">
-        <v>14.73334678831316</v>
       </c>
       <c r="E10" t="n">
         <v>29.60549914709465</v>
@@ -1084,10 +1084,10 @@
         <v>100</v>
       </c>
       <c r="C11" t="n">
+        <v>20.24919489997657</v>
+      </c>
+      <c r="D11" t="n">
         <v>8.200609733428356</v>
-      </c>
-      <c r="D11" t="n">
-        <v>20.24919489997657</v>
       </c>
       <c r="E11" t="n">
         <v>18.50072254335259</v>
@@ -1145,10 +1145,10 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
+        <v>15.45866208828719</v>
+      </c>
+      <c r="D12" t="n">
         <v>6.10555127546399</v>
-      </c>
-      <c r="D12" t="n">
-        <v>15.45866208828719</v>
       </c>
       <c r="E12" t="n">
         <v>18.81038582552551</v>
@@ -1206,10 +1206,10 @@
         <v>111</v>
       </c>
       <c r="C13" t="n">
+        <v>11.82673330997226</v>
+      </c>
+      <c r="D13" t="n">
         <v>7.295972452648715</v>
-      </c>
-      <c r="D13" t="n">
-        <v>11.82673330997226</v>
       </c>
       <c r="E13" t="n">
         <v>20.09641306993106</v>
@@ -1267,10 +1267,10 @@
         <v>135</v>
       </c>
       <c r="C14" t="n">
+        <v>19.61465840414153</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.5875973338088</v>
-      </c>
-      <c r="D14" t="n">
-        <v>19.61465840414153</v>
       </c>
       <c r="E14" t="n">
         <v>23.48875897660984</v>
@@ -1328,10 +1328,10 @@
         <v>990</v>
       </c>
       <c r="C15" t="n">
+        <v>15.40455475411362</v>
+      </c>
+      <c r="D15" t="n">
         <v>8.778631369658774</v>
-      </c>
-      <c r="D15" t="n">
-        <v>15.40455475411362</v>
       </c>
       <c r="E15" t="n">
         <v>27.14673439025135</v>
@@ -1389,10 +1389,10 @@
         <v>920</v>
       </c>
       <c r="C16" t="n">
+        <v>24.19501343855277</v>
+      </c>
+      <c r="D16" t="n">
         <v>12.82170541954994</v>
-      </c>
-      <c r="D16" t="n">
-        <v>24.19501343855277</v>
       </c>
       <c r="E16" t="n">
         <v>23.62311418179442</v>
